--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484116_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484116_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.8231</v>
+        <v>9.1121</v>
       </c>
       <c r="E2" t="n">
-        <v>8.367800000000001</v>
+        <v>8.6569</v>
       </c>
       <c r="F2" t="n">
         <v>0.4552</v>
@@ -610,10 +610,10 @@
         <v>2.579</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9919</v>
+        <v>-0.7029</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2209</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U2" t="n">
         <v>-0.771</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>X. ISERN MAZA</t>
+          <t>G. SEVILLANO PUIG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9031</v>
+        <v>2.1961</v>
       </c>
       <c r="E3" t="n">
-        <v>1.778</v>
+        <v>2.7102</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1252</v>
+        <v>-0.5142</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2527</v>
+        <v>0.323</v>
       </c>
       <c r="H3" t="n">
-        <v>1.184</v>
+        <v>-3.9561</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.4368</v>
+        <v>4.2792</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3277</v>
+        <v>1.6725</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9678</v>
+        <v>-2.7102</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.64</v>
+        <v>4.3827</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5805</v>
+        <v>-1.3495</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2163</v>
+        <v>-1.246</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7967</v>
+        <v>-0.1035</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9919</v>
+        <v>0.5952</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.1822</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9919</v>
+        <v>2.7774</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0425</v>
+        <v>-0.7978</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2438</v>
+        <v>-0.0622</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2863</v>
+        <v>-0.7356</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2065</v>
+        <v>2.0757</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2065</v>
+        <v>3.2821</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. SEVILLANO PUIG</t>
+          <t>X. ISERN MAZA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3166</v>
+        <v>1.7232</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7466</v>
+        <v>1.7383</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.43</v>
+        <v>-0.0151</v>
       </c>
       <c r="G4" t="n">
-        <v>0.323</v>
+        <v>-0.2527</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.9561</v>
+        <v>1.184</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2792</v>
+        <v>-1.4368</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6725</v>
+        <v>0.3277</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.7102</v>
+        <v>0.9678</v>
       </c>
       <c r="L4" t="n">
-        <v>4.3827</v>
+        <v>-0.64</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3495</v>
+        <v>-0.5805</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.246</v>
+        <v>0.2163</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1035</v>
+        <v>-0.7967</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1822</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7774</v>
+        <v>0.9919</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6772</v>
+        <v>-0.2225</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0258</v>
+        <v>0.2041</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6514</v>
+        <v>-0.4266</v>
       </c>
       <c r="V4" t="n">
-        <v>2.0757</v>
+        <v>1.2065</v>
       </c>
       <c r="W4" t="n">
-        <v>3.2821</v>
+        <v>1.2065</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ALEXANDRE</t>
+          <t>V. CASTELLON MARTIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7806999999999999</v>
+        <v>0.9137</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2723</v>
+        <v>0.1508</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4916</v>
+        <v>0.7628</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0505</v>
+        <v>1.0048</v>
       </c>
       <c r="H5" t="n">
-        <v>0.277</v>
+        <v>-1.3557</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7735</v>
+        <v>2.3605</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1361</v>
+        <v>1.3132</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2525</v>
+        <v>-1.2999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8836000000000001</v>
+        <v>2.6131</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0856</v>
+        <v>-0.3084</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0244</v>
+        <v>-0.0558</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.11</v>
+        <v>-0.2526</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1984</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7855</v>
+        <v>1.5871</v>
       </c>
       <c r="S5" t="n">
-        <v>1.667</v>
+        <v>0.0397</v>
       </c>
       <c r="T5" t="n">
-        <v>2.12</v>
+        <v>0.5555</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.453</v>
+        <v>-0.5159</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.7384</v>
+        <v>0.266</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.7384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. CASTELLON MARTIN</t>
+          <t>A. TARRIDA TORRES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5248</v>
+        <v>-0.8421999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0135</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5384</v>
+        <v>-0.7548</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0048</v>
+        <v>-1.4137</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.3557</v>
+        <v>-1.5121</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3605</v>
+        <v>0.0984</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3132</v>
+        <v>0.1109</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.2999</v>
+        <v>0.0255</v>
       </c>
       <c r="L6" t="n">
-        <v>2.6131</v>
+        <v>0.0854</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3084</v>
+        <v>-1.5246</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0558</v>
+        <v>-1.5376</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2526</v>
+        <v>0.013</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3968</v>
+        <v>1.1903</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5871</v>
+        <v>1.1903</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3491</v>
+        <v>-0.3528</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3912</v>
+        <v>-0.1983</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7403</v>
+        <v>-0.1545</v>
       </c>
       <c r="V6" t="n">
-        <v>0.266</v>
+        <v>-0.266</v>
       </c>
       <c r="W6" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DUCH BELTRAN</t>
+          <t>A. ALEXANDRE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9919</v>
+        <v>-0.8878</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9919</v>
+        <v>-0.0314</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-0.8563</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1.0505</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.277</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.7735</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1.1361</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.2525</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-0.0856</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.0244</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9919</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.7855</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0.0014</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.8163</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.8177</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.7384</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.7384</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. TARRIDA TORRES</t>
+          <t>M. ESTEBAN CALVO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.203</v>
+        <v>-0.9621</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2518</v>
+        <v>-2.3719</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9510999999999999</v>
+        <v>1.4099</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4137</v>
+        <v>-1.8349</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5121</v>
+        <v>-1.1496</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0984</v>
+        <v>-0.6853</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1109</v>
+        <v>-0.9379999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0255</v>
+        <v>-0.4987</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0854</v>
+        <v>-0.4392</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5246</v>
+        <v>-0.897</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5376</v>
+        <v>-0.6509</v>
       </c>
       <c r="O8" t="n">
-        <v>0.013</v>
+        <v>-0.2461</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1903</v>
+        <v>0.9919</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1903</v>
+        <v>1.9838</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7136</v>
+        <v>-0.7936</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3627</v>
+        <v>-0.4421</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3509</v>
+        <v>-0.3515</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.266</v>
+        <v>0.6745</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.266</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. FONT RODRIGUEZ</t>
+          <t>A. DUCH BELTRAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3066</v>
+        <v>-0.9919</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7141999999999999</v>
+        <v>-0.9919</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0207</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3.7929</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4486</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>4.2416</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>3.8948</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8774999999999999</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3.0172</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1018</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3262</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.2244</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.1822</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1741</v>
+        <v>-0.9919</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9919</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4331</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5384</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1054</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.4842</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.0162</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X. GUIA HORMIGON</t>
+          <t>D. FONT RODRIGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3263</v>
+        <v>-1.0237</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6471</v>
+        <v>0.9409</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6792</v>
+        <v>-1.9646</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6846</v>
+        <v>3.7929</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5019</v>
+        <v>-0.4486</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1827</v>
+        <v>4.2416</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2896</v>
+        <v>3.8948</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3077</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5973000000000001</v>
+        <v>3.0172</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.395</v>
+        <v>-0.1018</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.8097</v>
+        <v>-1.3262</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4146</v>
+        <v>1.2244</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3968</v>
+        <v>-2.1822</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1984</v>
+        <v>-3.1741</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3044</v>
+        <v>-0.1502</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4251</v>
+        <v>-0.3117</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1207</v>
+        <v>0.1615</v>
       </c>
       <c r="V10" t="n">
-        <v>0.266</v>
+        <v>-2.4842</v>
       </c>
       <c r="W10" t="n">
-        <v>0.266</v>
+        <v>0.532</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-3.0162</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. ESTEBAN CALVO</t>
+          <t>X. GUIA HORMIGON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5051</v>
+        <v>-1.1735</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.8027</v>
+        <v>-0.5224</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2976</v>
+        <v>-0.6511</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8349</v>
+        <v>-1.6846</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1496</v>
+        <v>-1.5019</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6853</v>
+        <v>-0.1827</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9379999999999999</v>
+        <v>-0.2896</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4987</v>
+        <v>0.3077</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.4392</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.897</v>
+        <v>-1.395</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6509</v>
+        <v>-1.8097</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2461</v>
+        <v>0.4146</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9919</v>
+        <v>0.3968</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9919</v>
+        <v>-0.1984</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9838</v>
+        <v>0.5952</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3366</v>
+        <v>-0.1516</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8728</v>
+        <v>-0.3004</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4637</v>
+        <v>0.1488</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6745</v>
+        <v>0.266</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8536</v>
+        <v>-1.6549</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7014</v>
+        <v>-0.4747</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1522</v>
+        <v>-1.1802</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9053</v>
@@ -1390,13 +1390,13 @@
         <v>1.3887</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1547</v>
+        <v>0.0439</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6121</v>
+        <v>-0.3854</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4574</v>
+        <v>0.4293</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.161799999999999</v>
+        <v>6.408999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>8.470500000000001</v>
+        <v>9.717299999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.308399999999999</v>
+        <v>-3.3084</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6643000000000001</v>
+        <v>0.6642999999999999</v>
       </c>
       <c r="H13" t="n">
         <v>-11.4166</v>
@@ -1444,7 +1444,7 @@
         <v>10.0512</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.515</v>
+        <v>-2.514999999999999</v>
       </c>
       <c r="L13" t="n">
         <v>12.5662</v>
@@ -1453,13 +1453,13 @@
         <v>-9.387</v>
       </c>
       <c r="N13" t="n">
-        <v>-8.901900000000001</v>
+        <v>-8.901899999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4851000000000001</v>
+        <v>-0.4851000000000003</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9919999999999999</v>
+        <v>0.9919999999999997</v>
       </c>
       <c r="Q13" t="n">
         <v>-14.8786</v>
@@ -1468,13 +1468,13 @@
         <v>15.8708</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.3361</v>
+        <v>-3.0892</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3028</v>
+        <v>-0.05609999999999998</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.0331</v>
+        <v>-3.0332</v>
       </c>
       <c r="V13" t="n">
         <v>7.8421</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2476</v>
+        <v>2.1634</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4675</v>
+        <v>2.0594</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2199</v>
+        <v>0.1041</v>
       </c>
       <c r="G14" t="n">
         <v>-2.0999</v>
@@ -1546,13 +1546,13 @@
         <v>2.9758</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9245</v>
+        <v>0.8403</v>
       </c>
       <c r="T14" t="n">
-        <v>0.771</v>
+        <v>0.3629</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1535</v>
+        <v>0.4774</v>
       </c>
       <c r="V14" t="n">
         <v>2.6295</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. LORAS MONTERO</t>
+          <t>T. KOHAN LÓPEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8361</v>
+        <v>1.1033</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3257</v>
+        <v>1.1425</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5104</v>
+        <v>-0.0393</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6069</v>
+        <v>0.9361</v>
       </c>
       <c r="H15" t="n">
-        <v>3.0798</v>
+        <v>0.5189</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.473</v>
+        <v>0.4172</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5006</v>
+        <v>0.7231</v>
       </c>
       <c r="K15" t="n">
-        <v>3.0603</v>
+        <v>0.0403</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5597</v>
+        <v>0.6827</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8937</v>
+        <v>0.213</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0195</v>
+        <v>0.4786</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9133</v>
+        <v>-0.2656</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.9838</v>
+        <v>0.1984</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.1661</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1822</v>
+        <v>0.1984</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0678</v>
+        <v>-0.0312</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2528</v>
+        <v>0.4195</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8149999999999999</v>
+        <v>-0.4506</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1453</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7384</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.5931</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. KOHAN LÓPEZ</t>
+          <t>D. LORAS MONTERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6391</v>
+        <v>0.9417</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.4075</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0954</v>
+        <v>0.5342</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9361</v>
+        <v>1.6069</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5189</v>
+        <v>3.0798</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4172</v>
+        <v>-1.473</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7231</v>
+        <v>2.5006</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0403</v>
+        <v>3.0603</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6827</v>
+        <v>-0.5597</v>
       </c>
       <c r="M16" t="n">
-        <v>0.213</v>
+        <v>-0.8937</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4786</v>
+        <v>0.0195</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2656</v>
+        <v>-0.9133</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1984</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-4.1661</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1984</v>
+        <v>2.1822</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4954</v>
+        <v>1.1733</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0113</v>
+        <v>0.3345</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5067</v>
+        <v>0.8388</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1453</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.7384</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.5931</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.06909999999999999</v>
+        <v>0.6655</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0827</v>
+        <v>1.1848</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1518</v>
+        <v>-0.5193</v>
       </c>
       <c r="G17" t="n">
         <v>0.3128</v>
@@ -1780,13 +1780,13 @@
         <v>1.7855</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4965</v>
+        <v>0.2381</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1418</v>
+        <v>0.2438</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6383</v>
+        <v>-0.0057</v>
       </c>
       <c r="V17" t="n">
         <v>-1.4724</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.298</v>
+        <v>-0.2062</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1339</v>
+        <v>0.338</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4319</v>
+        <v>-0.5441</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2855</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0125</v>
+        <v>0.0794</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1133</v>
+        <v>0.0907</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1009</v>
+        <v>-0.0113</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. BUSCAIL BRIANSO</t>
+          <t>A. DUCH BELTRAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.429</v>
+        <v>-0.2297</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2014</v>
+        <v>1.1017</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7724</v>
+        <v>-1.3314</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8506</v>
+        <v>-0.0038</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5446</v>
+        <v>-1.013</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3952</v>
+        <v>1.0091</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5022</v>
+        <v>1.7831</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2207</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7229</v>
+        <v>2.337</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3528</v>
+        <v>-1.7869</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7653</v>
+        <v>-0.459</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.1181</v>
+        <v>-1.3279</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1984</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1822</v>
+        <v>-1.9838</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3806</v>
+        <v>1.1903</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8978</v>
+        <v>0.4223</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1531</v>
+        <v>-0.17</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7446</v>
+        <v>0.5923</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6745</v>
+        <v>0.1453</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6745</v>
+        <v>1.4724</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.3271</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. DUCH BELTRAN</t>
+          <t>M. BUSCAIL BRIANSO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8164</v>
+        <v>-0.3575</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7956</v>
+        <v>-2.2014</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.612</v>
+        <v>1.8439</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0038</v>
+        <v>-0.8506</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.013</v>
+        <v>0.5446</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0091</v>
+        <v>-1.3952</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7831</v>
+        <v>0.5022</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.2207</v>
       </c>
       <c r="L20" t="n">
-        <v>2.337</v>
+        <v>0.7229</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7869</v>
+        <v>-1.3528</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.459</v>
+        <v>0.7653</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3279</v>
+        <v>-2.1181</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7935</v>
+        <v>0.1984</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9838</v>
+        <v>-2.1822</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1903</v>
+        <v>2.3806</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1643</v>
+        <v>0.9692</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4761</v>
+        <v>0.1531</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3117</v>
+        <v>0.8161</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1453</v>
+        <v>-0.6745</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4724</v>
+        <v>-0.6745</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.3271</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.063</v>
+        <v>-0.4628</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2404</v>
+        <v>0.6485</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3034</v>
+        <v>-1.1113</v>
       </c>
       <c r="G21" t="n">
         <v>0.2882</v>
@@ -2092,13 +2092,13 @@
         <v>0.3968</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7561</v>
+        <v>-0.1559</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1133</v>
+        <v>0.2948</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6428</v>
+        <v>-0.4506</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7674</v>
+        <v>-1.4375</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9736</v>
+        <v>-0.6676</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7938</v>
+        <v>-0.77</v>
       </c>
       <c r="G22" t="n">
         <v>-1.206</v>
@@ -2170,13 +2170,13 @@
         <v>0.5952</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0499</v>
+        <v>0.3798</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.289</v>
+        <v>0.0171</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3389</v>
+        <v>0.3627</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2065</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9283</v>
+        <v>-1.6664</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2913</v>
+        <v>-0.1893</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.637</v>
+        <v>-1.4771</v>
       </c>
       <c r="G23" t="n">
         <v>-0.0968</v>
@@ -2248,13 +2248,13 @@
         <v>2.1822</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9681</v>
+        <v>1.23</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2268</v>
+        <v>0.3289</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7413</v>
+        <v>0.9011</v>
       </c>
       <c r="V23" t="n">
         <v>-2.7996</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.5136</v>
+        <v>-3.6352</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0055</v>
+        <v>-0.5157</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.508</v>
+        <v>-3.1195</v>
       </c>
       <c r="G24" t="n">
         <v>0.7346</v>
@@ -2326,13 +2326,13 @@
         <v>0.9919</v>
       </c>
       <c r="S24" t="n">
-        <v>1.353</v>
+        <v>1.2314</v>
       </c>
       <c r="T24" t="n">
-        <v>1.4681</v>
+        <v>0.958</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1151</v>
+        <v>0.2734</v>
       </c>
       <c r="V24" t="n">
         <v>-4.6092</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.161999999999999</v>
+        <v>-3.1214</v>
       </c>
       <c r="E25" t="n">
-        <v>3.308399999999999</v>
+        <v>3.3084</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.470400000000001</v>
+        <v>-6.4298</v>
       </c>
       <c r="G25" t="n">
         <v>-0.6639999999999996</v>
@@ -2383,7 +2383,7 @@
         <v>8.9017</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4851000000000004</v>
+        <v>0.4851</v>
       </c>
       <c r="M25" t="n">
         <v>-10.051</v>
@@ -2395,7 +2395,7 @@
         <v>-12.5663</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.9918000000000005</v>
+        <v>-0.9918</v>
       </c>
       <c r="Q25" t="n">
         <v>-15.8706</v>
@@ -2404,13 +2404,13 @@
         <v>14.8789</v>
       </c>
       <c r="S25" t="n">
-        <v>4.3363</v>
+        <v>6.3767</v>
       </c>
       <c r="T25" t="n">
-        <v>3.0332</v>
+        <v>3.0333</v>
       </c>
       <c r="U25" t="n">
-        <v>1.303</v>
+        <v>3.3436</v>
       </c>
       <c r="V25" t="n">
         <v>-7.8421</v>
